--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="266">
   <si>
     <t>_reportFile</t>
   </si>
@@ -91,13 +91,34 @@
     <t>https://www.toyotafinancial.com/us/en/accessibility.html</t>
   </si>
   <si>
+    <t>us/en/contact-us.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout"]</t>
+  </si>
+  <si>
+    <t>us/en/contact-us</t>
+  </si>
+  <si>
+    <t>content-page</t>
+  </si>
+  <si>
+    <t>2026-10-04T04:59:21.156Z</t>
+  </si>
+  <si>
+    <t>Contact Us | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/contact_us.html</t>
+  </si>
+  <si>
     <t>us/en/online-policies-and-agreements.report.json</t>
   </si>
   <si>
     <t>us/en/online-policies-and-agreements</t>
   </si>
   <si>
-    <t>2026-10-03T23:57:11.653Z</t>
+    <t>2026-10-04T04:00:51.111Z</t>
   </si>
   <si>
     <t>Online Policies and Agreements | Toyota Financial</t>
@@ -115,7 +136,7 @@
     <t>us/en/online-privacy-policy</t>
   </si>
   <si>
-    <t>2026-10-03T23:57:18.617Z</t>
+    <t>2026-10-04T04:00:56.551Z</t>
   </si>
   <si>
     <t>Online Privacy Policies | Toyota Financial</t>
@@ -188,9 +209,6 @@
   </si>
   <si>
     <t>us/en/planning-tools/get-started</t>
-  </si>
-  <si>
-    <t>content-page</t>
   </si>
   <si>
     <t>2026-10-04T02:50:21.226Z</t>
@@ -1185,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -1295,7 +1313,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -1304,30 +1322,30 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -1336,7 +1354,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -1345,21 +1363,21 @@
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1368,7 +1386,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -1377,21 +1395,21 @@
         <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -1400,30 +1418,30 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -1502,24 +1520,24 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
         <v>66</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>67</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>68</v>
-      </c>
-      <c r="J10" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1534,24 +1552,24 @@
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -1560,30 +1578,30 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1592,30 +1610,30 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -1624,30 +1642,30 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1656,30 +1674,30 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1688,30 +1706,30 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1720,30 +1738,30 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -1752,30 +1770,30 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1784,30 +1802,30 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1816,30 +1834,30 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1848,30 +1866,30 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1880,30 +1898,30 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1912,30 +1930,30 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1944,30 +1962,30 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1976,30 +1994,30 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -2008,30 +2026,30 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J26" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2040,30 +2058,30 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J27" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -2072,30 +2090,30 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -2104,30 +2122,30 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -2136,30 +2154,30 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -2168,30 +2186,30 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J31" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2200,30 +2218,30 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2232,30 +2250,30 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2264,30 +2282,30 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2296,30 +2314,30 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2328,30 +2346,30 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2360,30 +2378,30 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2392,30 +2410,30 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2424,30 +2442,30 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2456,30 +2474,30 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2488,30 +2506,30 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -2520,30 +2538,30 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -2552,30 +2570,30 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -2584,30 +2602,30 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I44" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -2616,30 +2634,30 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -2648,30 +2666,30 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H46" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -2680,54 +2698,86 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H47" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
         <v>256</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>72</v>
+      </c>
+      <c r="H48" t="s">
         <v>257</v>
       </c>
-      <c r="F48" t="s">
+      <c r="I48" t="s">
         <v>258</v>
       </c>
-      <c r="G48" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
         <v>259</v>
       </c>
-      <c r="I48" t="s">
-        <v>12</v>
-      </c>
-      <c r="J48" t="s">
-        <v>69</v>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>260</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>261</v>
+      </c>
+      <c r="D49" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" t="s">
+        <v>263</v>
+      </c>
+      <c r="F49" t="s">
+        <v>264</v>
+      </c>
+      <c r="G49" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" t="s">
+        <v>265</v>
+      </c>
+      <c r="I49" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="356">
   <si>
     <t>_reportFile</t>
   </si>
@@ -145,6 +145,24 @@
     <t>https://www.toyotafinancial.com/us/en/online_privacy_policy.html</t>
   </si>
   <si>
+    <t>us/en/tfs-thoughtfuel-blog.report.json</t>
+  </si>
+  <si>
+    <t>["columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card","columns-card"]</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:06:26.543Z</t>
+  </si>
+  <si>
+    <t>TFS ThoughtFuel Blog | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog.html</t>
+  </si>
+  <si>
     <t>us/en/about-us/company-overview.report.json</t>
   </si>
   <si>
@@ -163,6 +181,60 @@
     <t>https://www.toyotafinancial.com/us/en/about_us/company_overview.html</t>
   </si>
   <si>
+    <t>us/en/financing-options/buy-a-toyota.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout","columns-callout","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/buy-a-toyota</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:04:38.180Z</t>
+  </si>
+  <si>
+    <t>Buy a Toyota | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/buy_a_toyota.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/leasing-a-toyota.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout","columns-callout","accordion-faq","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/leasing-a-toyota</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:04:43.836Z</t>
+  </si>
+  <si>
+    <t>Lease a Toyota | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/leasing_a_toyota.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/toyota-rewards-visa.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/toyota-rewards-visa</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:06:21.243Z</t>
+  </si>
+  <si>
+    <t>Toyota Rewards Visa | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/toyota_rewards_visa.html</t>
+  </si>
+  <si>
     <t>us/en/fragments/faq-help.report.json</t>
   </si>
   <si>
@@ -181,6 +253,27 @@
     <t>https://www.toyotafinancial.com/us/en/planning_tools/faq/Guaranteed_Auto_Protection_GAP.html</t>
   </si>
   <si>
+    <t>us/en/planning-tools/apply-for-credit.report.json</t>
+  </si>
+  <si>
+    <t>["embed-app"]</t>
+  </si>
+  <si>
+    <t>us/en/planning-tools/apply-for-credit</t>
+  </si>
+  <si>
+    <t>apply-for-credit</t>
+  </si>
+  <si>
+    <t>2026-10-04T05:05:55.110Z</t>
+  </si>
+  <si>
+    <t>Apply for Credit | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/planning_tools/apply_for_credit.html</t>
+  </si>
+  <si>
     <t>us/en/planning-tools/faq.report.json</t>
   </si>
   <si>
@@ -220,6 +313,192 @@
     <t>https://www.toyotafinancial.com/us/en/planning_tools/get_started.html</t>
   </si>
   <si>
+    <t>us/en/planning-tools/ways-to-pay.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","accordion-boxed","accordion-boxed","accordion-boxed","accordion-boxed","accordion-boxed","accordion-boxed","accordion-boxed"]</t>
+  </si>
+  <si>
+    <t>us/en/planning-tools/ways-to-pay</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:04:33.230Z</t>
+  </si>
+  <si>
+    <t>Ways to Pay | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/planning_tools/ways_to_pay.html</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/guaranteed-auto-protection.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout","video-poster"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/guaranteed-auto-protection</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:03:13.602Z</t>
+  </si>
+  <si>
+    <t>Guaranteed Auto Protection | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/guaranteed_auto_protection.html</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/prepaid-maintenance-plan.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","video-poster","table-caption","table-caption","table-caption","table-caption","table-caption","table-caption","table-caption","tabs-plans","tabs-plans","tabs-plans"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/prepaid-maintenance-plan</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:03:19.009Z</t>
+  </si>
+  <si>
+    <t>Prepaid Maintenance Plans | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/prepaid_maintenance_plan.html</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/tire-wheel-protection.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","accordion-faq","accordion-faq","accordion-faq","video-poster","table-caption","table-caption","tabs-plans"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/tire-wheel-protection</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:03:26.503Z</t>
+  </si>
+  <si>
+    <t>Tire &amp; Wheel Protection | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/tire_wheel_protection.html</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/vehicle-service-agreements.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","columns-callout","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","video-poster","tabs-plans","tabs-plans","tabs-plans","tabs-plans","tabs-plans"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/vehicle-service-agreements</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:03:04.477Z</t>
+  </si>
+  <si>
+    <t>Vehicle Service Agreements | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/vehicle_service_agreements.html</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/which-plan-is-right-for-me.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","video-poster","quiz-plans","carousel-cards"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/which-plan-is-right-for-me</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:02:57.966Z</t>
+  </si>
+  <si>
+    <t>Which plan is right for me? | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/which_plan_is_right_for_me.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/for-businesses/business-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/for-businesses/business-solutions</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:06:16.167Z</t>
+  </si>
+  <si>
+    <t>Business Solutions | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/for_businesses/business_solutions.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs/find-rebate-finance-programs.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs/find-rebate-finance-programs</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:04:51.364Z</t>
+  </si>
+  <si>
+    <t>Find a Program | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/rebate_finance_programs/find_rebate_finance_programs.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs/repeat-customers.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs/repeat-customers</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:04:57.928Z</t>
+  </si>
+  <si>
+    <t>Repeat Customers | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/rebate_finance_programs/repeat_customers.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/understanding-credit/credit-101.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/understanding-credit/credit-101</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:06:04.024Z</t>
+  </si>
+  <si>
+    <t>Credit 101 | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/understanding_credit/credit_101.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/understanding-credit/credit-tips.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/understanding-credit/credit-tips</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:06:09.456Z</t>
+  </si>
+  <si>
+    <t>Credit Tips | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/understanding_credit/credit_tips.html</t>
+  </si>
+  <si>
     <t>us/en/planning-tools/faq/about-credit.report.json</t>
   </si>
   <si>
@@ -340,9 +619,6 @@
     <t>2026-10-03T23:52:08.098Z</t>
   </si>
   <si>
-    <t>Business Solutions | Toyota Financial</t>
-  </si>
-  <si>
     <t>https://www.toyotafinancial.com/us/en/planning_tools/faq/business_solutions.html</t>
   </si>
   <si>
@@ -445,9 +721,6 @@
     <t>2026-10-03T23:54:35.448Z</t>
   </si>
   <si>
-    <t>Vehicle Service Agreements | Toyota Financial</t>
-  </si>
-  <si>
     <t>https://www.toyotafinancial.com/us/en/planning_tools/faq/financing_and_protection_products.html</t>
   </si>
   <si>
@@ -710,9 +983,6 @@
   </si>
   <si>
     <t>2026-10-03T23:54:14.842Z</t>
-  </si>
-  <si>
-    <t>Repeat Customers | Toyota Financial</t>
   </si>
   <si>
     <t>https://www.toyotafinancial.com/us/en/planning_tools/faq/repeat_customers.html</t>
@@ -1203,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -1424,7 +1694,7 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
         <v>47</v>
@@ -1441,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -1450,13 +1720,13 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
         <v>53</v>
@@ -1488,33 +1758,33 @@
         <v>14</v>
       </c>
       <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
         <v>59</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>60</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>61</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
         <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>65</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -1523,85 +1793,85 @@
         <v>29</v>
       </c>
       <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
         <v>66</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
         <v>69</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
         <v>70</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
         <v>71</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>72</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>73</v>
-      </c>
-      <c r="I11" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
         <v>76</v>
       </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
         <v>77</v>
       </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>78</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>79</v>
-      </c>
-      <c r="J12" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
         <v>81</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1616,24 +1886,24 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -1642,30 +1912,30 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1674,30 +1944,30 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1706,30 +1976,30 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1738,30 +2008,30 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H17" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I17" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J17" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -1770,30 +2040,30 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J18" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1802,30 +2072,30 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J19" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1834,30 +2104,30 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H20" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J20" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1866,30 +2136,30 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="J21" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1898,30 +2168,30 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H22" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="I22" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="J22" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1930,30 +2200,30 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H23" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I23" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="J23" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1962,30 +2232,30 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H24" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="I24" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1994,30 +2264,30 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I25" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -2026,30 +2296,30 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H26" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="I26" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J26" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2058,30 +2328,30 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H27" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="I27" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="J27" t="s">
-        <v>55</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -2090,30 +2360,30 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="J28" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -2122,30 +2392,30 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H29" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="I29" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="J29" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -2154,30 +2424,30 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H30" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="I30" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="J30" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -2186,30 +2456,30 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="I31" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="J31" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2218,30 +2488,30 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H32" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="I32" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="J32" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2250,30 +2520,30 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H33" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I33" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J33" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2282,30 +2552,30 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H34" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="I34" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="J34" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2314,30 +2584,30 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H35" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I35" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="J35" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2346,30 +2616,30 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H36" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="I36" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="J36" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2378,30 +2648,30 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H37" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="I37" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J37" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2410,30 +2680,30 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H38" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="I38" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="J38" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2442,30 +2712,30 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H39" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="I39" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="J39" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2474,30 +2744,30 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H40" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="I40" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="J40" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2506,30 +2776,30 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H41" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="I41" t="s">
-        <v>223</v>
+        <v>128</v>
       </c>
       <c r="J41" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -2538,30 +2808,30 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H42" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I42" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="J42" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -2570,30 +2840,30 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H43" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="I43" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="J43" t="s">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -2602,30 +2872,30 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H44" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I44" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="J44" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -2634,30 +2904,30 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H45" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="I45" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="J45" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -2666,30 +2936,30 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="I46" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="J46" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -2698,30 +2968,30 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H47" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I47" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="J47" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -2730,54 +3000,566 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H48" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I48" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="J48" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="C49" t="s">
-        <v>261</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>262</v>
+        <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F49" t="s">
-        <v>264</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="I49" t="s">
-        <v>12</v>
+        <v>274</v>
       </c>
       <c r="J49" t="s">
-        <v>75</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>276</v>
+      </c>
+      <c r="B50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>277</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" t="s">
+        <v>278</v>
+      </c>
+      <c r="I50" t="s">
+        <v>279</v>
+      </c>
+      <c r="J50" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>281</v>
+      </c>
+      <c r="B51" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>282</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>165</v>
+      </c>
+      <c r="H51" t="s">
+        <v>283</v>
+      </c>
+      <c r="I51" t="s">
+        <v>284</v>
+      </c>
+      <c r="J51" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>286</v>
+      </c>
+      <c r="B52" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>287</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>165</v>
+      </c>
+      <c r="H52" t="s">
+        <v>288</v>
+      </c>
+      <c r="I52" t="s">
+        <v>289</v>
+      </c>
+      <c r="J52" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>291</v>
+      </c>
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>292</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>165</v>
+      </c>
+      <c r="H53" t="s">
+        <v>293</v>
+      </c>
+      <c r="I53" t="s">
+        <v>294</v>
+      </c>
+      <c r="J53" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>296</v>
+      </c>
+      <c r="B54" t="s">
+        <v>163</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>297</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" t="s">
+        <v>298</v>
+      </c>
+      <c r="I54" t="s">
+        <v>299</v>
+      </c>
+      <c r="J54" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>301</v>
+      </c>
+      <c r="B55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>302</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>165</v>
+      </c>
+      <c r="H55" t="s">
+        <v>303</v>
+      </c>
+      <c r="I55" t="s">
+        <v>304</v>
+      </c>
+      <c r="J55" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>306</v>
+      </c>
+      <c r="B56" t="s">
+        <v>163</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>307</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>165</v>
+      </c>
+      <c r="H56" t="s">
+        <v>308</v>
+      </c>
+      <c r="I56" t="s">
+        <v>309</v>
+      </c>
+      <c r="J56" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>311</v>
+      </c>
+      <c r="B57" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>312</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>165</v>
+      </c>
+      <c r="H57" t="s">
+        <v>313</v>
+      </c>
+      <c r="I57" t="s">
+        <v>314</v>
+      </c>
+      <c r="J57" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>316</v>
+      </c>
+      <c r="B58" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>317</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>165</v>
+      </c>
+      <c r="H58" t="s">
+        <v>318</v>
+      </c>
+      <c r="I58" t="s">
+        <v>319</v>
+      </c>
+      <c r="J58" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>321</v>
+      </c>
+      <c r="B59" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>322</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>165</v>
+      </c>
+      <c r="H59" t="s">
+        <v>323</v>
+      </c>
+      <c r="I59" t="s">
+        <v>150</v>
+      </c>
+      <c r="J59" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>325</v>
+      </c>
+      <c r="B60" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>326</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>165</v>
+      </c>
+      <c r="H60" t="s">
+        <v>327</v>
+      </c>
+      <c r="I60" t="s">
+        <v>328</v>
+      </c>
+      <c r="J60" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>330</v>
+      </c>
+      <c r="B61" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>331</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>165</v>
+      </c>
+      <c r="H61" t="s">
+        <v>332</v>
+      </c>
+      <c r="I61" t="s">
+        <v>333</v>
+      </c>
+      <c r="J61" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>335</v>
+      </c>
+      <c r="B62" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>336</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>165</v>
+      </c>
+      <c r="H62" t="s">
+        <v>337</v>
+      </c>
+      <c r="I62" t="s">
+        <v>338</v>
+      </c>
+      <c r="J62" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>340</v>
+      </c>
+      <c r="B63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>341</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>165</v>
+      </c>
+      <c r="H63" t="s">
+        <v>342</v>
+      </c>
+      <c r="I63" t="s">
+        <v>343</v>
+      </c>
+      <c r="J63" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>345</v>
+      </c>
+      <c r="B64" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>346</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>165</v>
+      </c>
+      <c r="H64" t="s">
+        <v>347</v>
+      </c>
+      <c r="I64" t="s">
+        <v>348</v>
+      </c>
+      <c r="J64" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>350</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>351</v>
+      </c>
+      <c r="D65" t="s">
+        <v>352</v>
+      </c>
+      <c r="E65" t="s">
+        <v>353</v>
+      </c>
+      <c r="F65" t="s">
+        <v>354</v>
+      </c>
+      <c r="G65" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" t="s">
+        <v>355</v>
+      </c>
+      <c r="I65" t="s">
+        <v>12</v>
+      </c>
+      <c r="J65" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="382">
   <si>
     <t>_reportFile</t>
   </si>
@@ -313,6 +313,21 @@
     <t>https://www.toyotafinancial.com/us/en/planning_tools/get_started.html</t>
   </si>
   <si>
+    <t>us/en/planning-tools/visiting-the-dealer.report.json</t>
+  </si>
+  <si>
+    <t>us/en/planning-tools/visiting-the-dealer</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:11:09.563Z</t>
+  </si>
+  <si>
+    <t>Visiting the Dealer | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/planning_tools/visiting_the_dealer.html</t>
+  </si>
+  <si>
     <t>us/en/planning-tools/ways-to-pay.report.json</t>
   </si>
   <si>
@@ -349,6 +364,24 @@
     <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/guaranteed_auto_protection.html</t>
   </si>
   <si>
+    <t>us/en/vehicle-protection-plan/how-to-file-a-claim.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","tabs-plans"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/how-to-file-a-claim</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:16:49.792Z</t>
+  </si>
+  <si>
+    <t>How to File a Claim | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/how_to_file_a_claim.html</t>
+  </si>
+  <si>
     <t>us/en/vehicle-protection-plan/prepaid-maintenance-plan.report.json</t>
   </si>
   <si>
@@ -421,6 +454,21 @@
     <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/which_plan_is_right_for_me.html</t>
   </si>
   <si>
+    <t>us/en/financing-options/for-businesses/business-credit-applications.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/for-businesses/business-credit-applications</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:11:25.462Z</t>
+  </si>
+  <si>
+    <t>Business Credit Application | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/for_businesses/business_credit_applications.html</t>
+  </si>
+  <si>
     <t>us/en/financing-options/for-businesses/business-solutions.report.json</t>
   </si>
   <si>
@@ -439,6 +487,21 @@
     <t>https://www.toyotafinancial.com/us/en/financing_options/for_businesses/business_solutions.html</t>
   </si>
   <si>
+    <t>us/en/financing-options/rebate-finance-programs/college-rebate-program.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs/college-rebate-program</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:11:14.381Z</t>
+  </si>
+  <si>
+    <t>College Rebate Program | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/rebate_finance_programs/college_rebate_program.html</t>
+  </si>
+  <si>
     <t>us/en/financing-options/rebate-finance-programs/find-rebate-finance-programs.report.json</t>
   </si>
   <si>
@@ -452,6 +515,21 @@
   </si>
   <si>
     <t>https://www.toyotafinancial.com/us/en/financing_options/rebate_finance_programs/find_rebate_finance_programs.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs/military-rebate-program.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs/military-rebate-program</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:11:19.736Z</t>
+  </si>
+  <si>
+    <t>Military Rebate Program | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/rebate_finance_programs/military_rebate_program.html</t>
   </si>
   <si>
     <t>us/en/financing-options/rebate-finance-programs/repeat-customers.report.json</t>
@@ -1473,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -1967,16 +2045,16 @@
         <v>100</v>
       </c>
       <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
         <v>101</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
-        <v>102</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
@@ -1985,30 +2063,30 @@
         <v>29</v>
       </c>
       <c r="H16" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" t="s">
         <v>103</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>104</v>
-      </c>
-      <c r="J16" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
         <v>106</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
         <v>107</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
-        <v>108</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
@@ -2017,30 +2095,30 @@
         <v>29</v>
       </c>
       <c r="H17" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" t="s">
         <v>109</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>110</v>
-      </c>
-      <c r="J17" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" t="s">
         <v>112</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
         <v>113</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>114</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
@@ -2049,30 +2127,30 @@
         <v>29</v>
       </c>
       <c r="H18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" t="s">
         <v>115</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>116</v>
-      </c>
-      <c r="J18" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" t="s">
         <v>118</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
         <v>119</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>120</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
@@ -2081,30 +2159,30 @@
         <v>29</v>
       </c>
       <c r="H19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" t="s">
         <v>121</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>122</v>
-      </c>
-      <c r="J19" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="s">
         <v>124</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
         <v>125</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
-        <v>126</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
@@ -2113,30 +2191,30 @@
         <v>29</v>
       </c>
       <c r="H20" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" t="s">
         <v>127</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>128</v>
-      </c>
-      <c r="J20" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" t="s">
         <v>130</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
         <v>131</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>132</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
@@ -2145,30 +2223,30 @@
         <v>29</v>
       </c>
       <c r="H21" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" t="s">
         <v>133</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>134</v>
-      </c>
-      <c r="J21" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" t="s">
         <v>136</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
         <v>137</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>138</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
@@ -2177,21 +2255,21 @@
         <v>29</v>
       </c>
       <c r="H22" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" t="s">
         <v>139</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>140</v>
-      </c>
-      <c r="J22" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" t="s">
         <v>142</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -2223,7 +2301,7 @@
         <v>147</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -2255,7 +2333,7 @@
         <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -2264,7 +2342,7 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
@@ -2273,21 +2351,21 @@
         <v>29</v>
       </c>
       <c r="H25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -2296,7 +2374,7 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -2305,21 +2383,21 @@
         <v>29</v>
       </c>
       <c r="H26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2334,152 +2412,152 @@
         <v>14</v>
       </c>
       <c r="G27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" t="s">
         <v>165</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>166</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>167</v>
-      </c>
-      <c r="J27" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
         <v>169</v>
       </c>
-      <c r="B28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" t="s">
         <v>170</v>
       </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s">
-        <v>165</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>171</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>172</v>
-      </c>
-      <c r="J28" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
         <v>174</v>
       </c>
-      <c r="B29" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
         <v>175</v>
       </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>165</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>176</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>177</v>
-      </c>
-      <c r="J29" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
         <v>179</v>
       </c>
-      <c r="B30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C30" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" t="s">
         <v>180</v>
       </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" t="s">
-        <v>165</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>181</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>182</v>
-      </c>
-      <c r="J30" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
         <v>184</v>
       </c>
-      <c r="B31" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
         <v>185</v>
       </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" t="s">
-        <v>165</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>186</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>187</v>
-      </c>
-      <c r="J31" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B32" t="s">
         <v>189</v>
-      </c>
-      <c r="B32" t="s">
-        <v>163</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2494,24 +2572,24 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H32" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2520,30 +2598,30 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I33" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2552,30 +2630,30 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I34" t="s">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="J34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2584,30 +2662,30 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I35" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J35" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2616,30 +2694,30 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J36" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2648,30 +2726,30 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J37" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B38" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2680,30 +2758,30 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B39" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2712,30 +2790,30 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I39" t="s">
-        <v>226</v>
+        <v>156</v>
       </c>
       <c r="J39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B40" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2744,30 +2822,30 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I40" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B41" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2776,30 +2854,30 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I41" t="s">
-        <v>128</v>
+        <v>237</v>
       </c>
       <c r="J41" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B42" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -2808,30 +2886,30 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H42" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I42" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -2840,30 +2918,30 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H43" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I43" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J43" t="s">
-        <v>79</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -2872,30 +2950,30 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H44" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I44" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J44" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -2904,30 +2982,30 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H45" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I45" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J45" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -2936,30 +3014,30 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I46" t="s">
-        <v>259</v>
+        <v>139</v>
       </c>
       <c r="J46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -2968,30 +3046,30 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H47" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I47" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J47" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B48" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -3000,30 +3078,30 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H48" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I48" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J48" t="s">
-        <v>270</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B49" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
@@ -3032,30 +3110,30 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J49" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -3064,30 +3142,30 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B51" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -3096,30 +3174,30 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I51" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J51" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
@@ -3128,30 +3206,30 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H52" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I52" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J52" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B53" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -3160,30 +3238,30 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H53" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B54" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -3192,30 +3270,30 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H54" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I54" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J54" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
@@ -3224,30 +3302,30 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H55" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I55" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J55" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -3256,30 +3334,30 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H56" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I56" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J56" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -3288,30 +3366,30 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H57" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I57" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J57" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -3320,30 +3398,30 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I58" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B59" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -3352,30 +3430,30 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I59" t="s">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="J59" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
@@ -3384,30 +3462,30 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J60" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B61" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -3416,30 +3494,30 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H61" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I61" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J61" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -3448,30 +3526,30 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H62" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I62" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J62" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -3480,30 +3558,30 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H63" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I63" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J63" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
@@ -3512,54 +3590,214 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H64" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I64" t="s">
-        <v>348</v>
+        <v>176</v>
       </c>
       <c r="J64" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>189</v>
       </c>
       <c r="C65" t="s">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
         <v>352</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
+        <v>191</v>
+      </c>
+      <c r="H65" t="s">
         <v>353</v>
       </c>
-      <c r="F65" t="s">
+      <c r="I65" t="s">
         <v>354</v>
       </c>
-      <c r="G65" t="s">
-        <v>12</v>
-      </c>
-      <c r="H65" t="s">
+      <c r="J65" t="s">
         <v>355</v>
       </c>
-      <c r="I65" t="s">
-        <v>12</v>
-      </c>
-      <c r="J65" t="s">
-        <v>168</v>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>356</v>
+      </c>
+      <c r="B66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>357</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" t="s">
+        <v>191</v>
+      </c>
+      <c r="H66" t="s">
+        <v>358</v>
+      </c>
+      <c r="I66" t="s">
+        <v>359</v>
+      </c>
+      <c r="J66" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>361</v>
+      </c>
+      <c r="B67" t="s">
+        <v>189</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>362</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>191</v>
+      </c>
+      <c r="H67" t="s">
+        <v>363</v>
+      </c>
+      <c r="I67" t="s">
+        <v>364</v>
+      </c>
+      <c r="J67" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>366</v>
+      </c>
+      <c r="B68" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" t="s">
+        <v>367</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>191</v>
+      </c>
+      <c r="H68" t="s">
+        <v>368</v>
+      </c>
+      <c r="I68" t="s">
+        <v>369</v>
+      </c>
+      <c r="J68" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>371</v>
+      </c>
+      <c r="B69" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" t="s">
+        <v>372</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s">
+        <v>191</v>
+      </c>
+      <c r="H69" t="s">
+        <v>373</v>
+      </c>
+      <c r="I69" t="s">
+        <v>374</v>
+      </c>
+      <c r="J69" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>376</v>
+      </c>
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" t="s">
+        <v>377</v>
+      </c>
+      <c r="D70" t="s">
+        <v>378</v>
+      </c>
+      <c r="E70" t="s">
+        <v>379</v>
+      </c>
+      <c r="F70" t="s">
+        <v>380</v>
+      </c>
+      <c r="G70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" t="s">
+        <v>381</v>
+      </c>
+      <c r="I70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J70" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="726">
   <si>
     <t>_reportFile</t>
   </si>
@@ -112,6 +112,36 @@
     <t>https://www.toyotafinancial.com/us/en/contact_us.html</t>
   </si>
   <si>
+    <t>us/en/data-privacy-request.report.json</t>
+  </si>
+  <si>
+    <t>us/en/data-privacy-request</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:55.768Z</t>
+  </si>
+  <si>
+    <t>Data Privacy Request | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/data-privacy-request.html</t>
+  </si>
+  <si>
+    <t>us/en/glossary.report.json</t>
+  </si>
+  <si>
+    <t>us/en/glossary</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:40:23.249Z</t>
+  </si>
+  <si>
+    <t>Glossary | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/glossary.html</t>
+  </si>
+  <si>
     <t>us/en/online-policies-and-agreements.report.json</t>
   </si>
   <si>
@@ -145,6 +175,21 @@
     <t>https://www.toyotafinancial.com/us/en/online_privacy_policy.html</t>
   </si>
   <si>
+    <t>us/en/sitemap.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sitemap</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:28.989Z</t>
+  </si>
+  <si>
+    <t>Site Map | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/sitemap.html</t>
+  </si>
+  <si>
     <t>us/en/tfs-thoughtfuel-blog.report.json</t>
   </si>
   <si>
@@ -181,6 +226,129 @@
     <t>https://www.toyotafinancial.com/us/en/about_us/company_overview.html</t>
   </si>
   <si>
+    <t>us/en/end-of-lease-options/early-lease-return.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-circle","fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/early-lease-return</t>
+  </si>
+  <si>
+    <t>end-of-lease</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:38:39.870Z</t>
+  </si>
+  <si>
+    <t>Early Lease Return | Toyota Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/end_of_lease_options/early_lease_return.html</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/faqs.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-circle","accordion-circle","accordion-circle","fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/faqs</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:38:45.193Z</t>
+  </si>
+  <si>
+    <t>FAQs | Toyota Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/end_of_lease_options/faqs.html</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/lease-end-videos.report.json</t>
+  </si>
+  <si>
+    <t>["cards-video","fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/lease-end-videos</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:42:07.469Z</t>
+  </si>
+  <si>
+    <t>Lease-End Videos | Toyota Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/end_of_lease_options/lease-end-videos.html</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/mileage.report.json</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/mileage</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:38:57.350Z</t>
+  </si>
+  <si>
+    <t>Mileage | Toyota Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/end_of_lease_options/mileage.html</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/return-your-vehicle.report.json</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/return-your-vehicle</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:39:14.639Z</t>
+  </si>
+  <si>
+    <t>Return Your Vehicle | Toyota Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/end_of_lease_options/return_your_vehicle.html</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/wear-and-use.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-circle","accordion-circle","accordion-circle","accordion-circle","fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/wear-and-use</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:39:04.294Z</t>
+  </si>
+  <si>
+    <t>Wear &amp; Use | Toyota Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/end_of_lease_options/wear_and_use.html</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/your-option.report.json</t>
+  </si>
+  <si>
+    <t>["cards-steps","fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/end-of-lease-options/your-option</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:42:00.906Z</t>
+  </si>
+  <si>
+    <t>Your Options | Toyota Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/end_of_lease_options/your_option.html</t>
+  </si>
+  <si>
     <t>us/en/financing-options/buy-a-toyota.report.json</t>
   </si>
   <si>
@@ -199,6 +367,45 @@
     <t>https://www.toyotafinancial.com/us/en/financing_options/buy_a_toyota.html</t>
   </si>
   <si>
+    <t>us/en/financing-options/buy-or-lease.report.json</t>
+  </si>
+  <si>
+    <t>["quiz-buy-lease","columns-callout"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/buy-or-lease</t>
+  </si>
+  <si>
+    <t>buy-or-lease</t>
+  </si>
+  <si>
+    <t>2026-10-04T06:40:27.273Z</t>
+  </si>
+  <si>
+    <t>Buy or Lease Quiz | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/buy_or_lease.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/for-businesses.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/for-businesses</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:40:01.161Z</t>
+  </si>
+  <si>
+    <t>Business Solutions | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/for_businesses.html</t>
+  </si>
+  <si>
     <t>us/en/financing-options/leasing-a-toyota.report.json</t>
   </si>
   <si>
@@ -217,12 +424,27 @@
     <t>https://www.toyotafinancial.com/us/en/financing_options/leasing_a_toyota.html</t>
   </si>
   <si>
+    <t>us/en/financing-options/rebate-finance-programs.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","columns-callout"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/rebate-finance-programs</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:40:07.024Z</t>
+  </si>
+  <si>
+    <t>Find a Program | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/rebate_finance_programs.html</t>
+  </si>
+  <si>
     <t>us/en/financing-options/toyota-rewards-visa.report.json</t>
   </si>
   <si>
-    <t>["columns-callout","columns-callout"]</t>
-  </si>
-  <si>
     <t>us/en/financing-options/toyota-rewards-visa</t>
   </si>
   <si>
@@ -235,6 +457,39 @@
     <t>https://www.toyotafinancial.com/us/en/financing_options/toyota_rewards_visa.html</t>
   </si>
   <si>
+    <t>us/en/financing-options/understanding-credit.report.json</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/understanding-credit</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:40:11.311Z</t>
+  </si>
+  <si>
+    <t>Credit 101 | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/understanding_credit.html</t>
+  </si>
+  <si>
+    <t>us/en/fragments/blog-articles.report.json</t>
+  </si>
+  <si>
+    <t>us/en/fragments/blog-articles</t>
+  </si>
+  <si>
+    <t>blog-articles-fragment</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:34:29.633Z</t>
+  </si>
+  <si>
+    <t>Blog article list fragment</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Driving_Electric_What_to_Know_About_Protection_After_Your_Factory_Warranty_Ends.html</t>
+  </si>
+  <si>
     <t>us/en/fragments/faq-help.report.json</t>
   </si>
   <si>
@@ -253,6 +508,114 @@
     <t>https://www.toyotafinancial.com/us/en/planning_tools/faq/Guaranteed_Auto_Protection_GAP.html</t>
   </si>
   <si>
+    <t>us/en/fragments/lease-end-help.report.json</t>
+  </si>
+  <si>
+    <t>["columns-card","columns-callout"]</t>
+  </si>
+  <si>
+    <t>us/en/fragments/lease-end-help</t>
+  </si>
+  <si>
+    <t>lease-end-help-fragment</t>
+  </si>
+  <si>
+    <t>2026-10-04T07:38:04.077Z</t>
+  </si>
+  <si>
+    <t>Lease-end help fragment</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/about-toyota.report.json</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/about-toyota</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:40:28.885Z</t>
+  </si>
+  <si>
+    <t>About Toyota | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/investor_relations/about_toyota.html</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/asset-backed-securities.report.json</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/asset-backed-securities</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:00.714Z</t>
+  </si>
+  <si>
+    <t>Asset-Backed Securities | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/investor_relations/asset-backed_securities.html</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/company-presentations.report.json</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/company-presentations</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:04.845Z</t>
+  </si>
+  <si>
+    <t>Company Presentations | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/investor_relations/company_presentations.html</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/sales-and-trading.report.json</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/sales-and-trading</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:10.053Z</t>
+  </si>
+  <si>
+    <t>Sales and Trading | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/investor_relations/sales_and_trading.html</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/sec-filings.report.json</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/sec-filings</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:15.794Z</t>
+  </si>
+  <si>
+    <t>SEC Filings | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/investor_relations/sec_filings.html</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/unsecured-term-debt.report.json</t>
+  </si>
+  <si>
+    <t>us/en/investor-relations/unsecured-term-debt</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:23.295Z</t>
+  </si>
+  <si>
+    <t>Unsecured Term Debt | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/investor_relations/unsecured_term_debt.html</t>
+  </si>
+  <si>
     <t>us/en/planning-tools/apply-for-credit.report.json</t>
   </si>
   <si>
@@ -346,6 +709,609 @@
     <t>https://www.toyotafinancial.com/us/en/planning_tools/ways_to_pay.html</t>
   </si>
   <si>
+    <t>us/en/tfs-thoughtfuel-blog/a-lease-story-patrick-mahoney-and-his-2021-rav4-xse-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/a-lease-story-patrick-mahoney-and-his-2021-rav4-xse-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:40.591Z</t>
+  </si>
+  <si>
+    <t>A Lease Story: Patrick Mahoney and His RAV4 XSE Hybrid | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/a_lease_story_patrick_mahoney_and_his_2021_RAV4_XSE_hybrid.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/be-prepared-for-safe-winter-driving.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/be-prepared-for-safe-winter-driving</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:46.364Z</t>
+  </si>
+  <si>
+    <t>Be Prepared for Safe Winter Driving | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/be_prepared_for_safe_winter_driving.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/buying-your-first-car.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/buying-your-first-car</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:51.123Z</t>
+  </si>
+  <si>
+    <t>Buying Your First Car | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/buying_your_first_car.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/celebrating-40-years.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","video-poster","fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/celebrating-40-years</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:57.917Z</t>
+  </si>
+  <si>
+    <t>Celebrating 40 Years | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/celebrating_40_years.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/demystifying-apr.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/demystifying-apr</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:04.007Z</t>
+  </si>
+  <si>
+    <t>Demystifying APR | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/demystifying_apr.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/driving-electric-what-to-know-about-protection-after-your-factory-warranty-ends.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/driving-electric-what-to-know-about-protection-after-your-factory-warranty-ends</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:15.956Z</t>
+  </si>
+  <si>
+    <t>Driving Electric? What to Know About Protection After Your Factory Warranty Ends | Toyota Financial</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/factors-that-affect-auto-insurance-rates.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/factors-that-affect-auto-insurance-rates</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:21.055Z</t>
+  </si>
+  <si>
+    <t>Factors that Affect Auto Insurance Rates | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Factors_that_Affect_Auto_Insurance_Rates.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/getting-back-on-your-feet.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/getting-back-on-your-feet</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:08.764Z</t>
+  </si>
+  <si>
+    <t>Getting Back on Your Feet | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/getting-back-on-your-feet.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-maintain-your-toyota.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-maintain-your-toyota</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:26.701Z</t>
+  </si>
+  <si>
+    <t>How to Maintain Your Toyota | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/How-to-maintain-your-toyota.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-maximize-the-resale-value-of-your-vehicle.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-maximize-the-resale-value-of-your-vehicle</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:24.530Z</t>
+  </si>
+  <si>
+    <t>How to Maximize the Resale Value of Your Vehicle | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/how_to_maximize_the_resale_value_of_your_vehicle.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-prepare-financially-for-a-natural-disaster.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-prepare-financially-for-a-natural-disaster</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:13.879Z</t>
+  </si>
+  <si>
+    <t>How to Prepare Financially for a Natural Disaster | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/how-to-prepare-financially-for-a-natural-disaster.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-protect-your-toyota.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-protect-your-toyota</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:30.723Z</t>
+  </si>
+  <si>
+    <t>How To Protect Your Toyota | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/how_to_protect_your_toyota.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-read-a-billing-statement.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/how-to-read-a-billing-statement</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:19.852Z</t>
+  </si>
+  <si>
+    <t>How to Read a Billing Statement | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/how-to-read-a-billing-statement.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/keys-have-a-way-of-disappearing.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/keys-have-a-way-of-disappearing</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:33.177Z</t>
+  </si>
+  <si>
+    <t>Keys Have a Way of Disappearing | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Keys-Have-a-Way-of-Disappearing.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/leasing-or-owning-a-new-or-certified-used-toyota.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/leasing-or-owning-a-new-or-certified-used-toyota</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:37.068Z</t>
+  </si>
+  <si>
+    <t>Leasing or Owning a New or Certified-Used Toyota | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/leasing_or_owning_a_new_or_certified_used_toyota.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/leasing-terminology.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/leasing-terminology</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:43.539Z</t>
+  </si>
+  <si>
+    <t>Leasing Terminology | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/leasing_terminology.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/nine-easy-ways-to-reduce-fuel-consumption.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/nine-easy-ways-to-reduce-fuel-consumption</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:49.222Z</t>
+  </si>
+  <si>
+    <t>Nine Easy Ways to Reduce Fuel Consumption | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/nine-easy-ways-to-reduce-fuel-consumption.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/principal-only-payments.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/principal-only-payments</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:38.604Z</t>
+  </si>
+  <si>
+    <t>Principal-Only Payments | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Principal-Only-Payments.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/protect-yourself-from-identity-theft-online.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/protect-yourself-from-identity-theft-online</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:44.935Z</t>
+  </si>
+  <si>
+    <t>Protect Yourself from Identity Theft Online: Tips for Securing Your Accounts | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Protect_Yourself_from_Identity_Theft_Online.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/purchase-your-toyota-at-lease-end.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/purchase-your-toyota-at-lease-end</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:55.051Z</t>
+  </si>
+  <si>
+    <t>Purchase Your Toyota at Lease-End | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/purchase-your-toyota-at-lease-end.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/setting-up-recurring-payments.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/setting-up-recurring-payments</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:11.620Z</t>
+  </si>
+  <si>
+    <t>Setting Up Recurring Payments | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog//setting-up-recurring-payments.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/take-a-drive-through-your-online-account.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/take-a-drive-through-your-online-account</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:38:59.519Z</t>
+  </si>
+  <si>
+    <t>Convenient. Secure. Sustainable. Take a Drive Through Your Online Account | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/take-a-drive-through-your-online-account.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/ten-tips-for-driving-at-night.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/ten-tips-for-driving-at-night</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:50.765Z</t>
+  </si>
+  <si>
+    <t>Ten Tips for Driving at Night  | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Ten_Tips_for_Driving_at_Night.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/the-ins-and-outs-of-auto-insurance.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/the-ins-and-outs-of-auto-insurance</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:12.578Z</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/the_ins_and_outs_of_auto_insurance.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/the-lease-end-process.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/the-lease-end-process</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:05.806Z</t>
+  </si>
+  <si>
+    <t>The Lease-End Process | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/the-Lease-end-process.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/top-reasons-to-choose-toyota-family-vehicle.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/top-reasons-to-choose-toyota-family-vehicle</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:18.149Z</t>
+  </si>
+  <si>
+    <t>Top Reasons to Choose Toyota for Your Next Family Vehicle | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/top-reasons-to-choose-toyota-family-vehicle.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/top-reasons-to-consider-buying-a-used-or-certified-pre-owned-cpo-vehicle.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/top-reasons-to-consider-buying-a-used-or-certified-pre-owned-cpo-vehicle</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:36:57.225Z</t>
+  </si>
+  <si>
+    <t>Top Reasons to Consider Buying a Used or Certified Pre-Owned (CPO) Vehicle | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Top-Reasons-to-Consider-Buying-a-Used-or-Certified-Pre-Owned-CPO-Vehicle.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/toyota-financial-services-is-on-instagram.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/toyota-financial-services-is-on-instagram</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:22.315Z</t>
+  </si>
+  <si>
+    <t>Toyota Financial Services is on Instagram | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/toyota-financial-services-is-on-instagram.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/toyota-owner-profile-kelly-davis.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/toyota-owner-profile-kelly-davis</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:03.993Z</t>
+  </si>
+  <si>
+    <t>Toyota Owner Profile Kelly Davis: How Two Long-Time Toyota Fans Stay Protected | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Toyota_Owner_Profile_Kelly_Davis.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/toyota-owner-profile-sean-ross.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/toyota-owner-profile-sean-ross</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:09.552Z</t>
+  </si>
+  <si>
+    <t>Toyota Owner Profile Sean Ross: Five Toyotas, Loads of Adventure and Plenty of Peace of Mind | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Toyota_Owner_Profile_Sean_Ross.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/we-love-new-grads-lets-get-you-behind-the-wheel.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/we-love-new-grads-lets-get-you-behind-the-wheel</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:14.722Z</t>
+  </si>
+  <si>
+    <t>We Love New Grads. Let’s Get You Behind the Wheel. | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/We_Love_New_Grads_Lets_Get_You_Behind_the_Wheel.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/weighing-your-options-buy-vs-lease.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/weighing-your-options-buy-vs-lease</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:19.337Z</t>
+  </si>
+  <si>
+    <t>Weighing Your Options: Buy vs. Lease | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Weighing_Your_Options_Buy_vs_Lease.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/what-to-expect-from-toyota-test-drive.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/what-to-expect-from-toyota-test-drive</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:28.427Z</t>
+  </si>
+  <si>
+    <t>What to Expect from a Toyota Test Drive Experience | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/what-to-expect-from-toyota-test-drive.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/when-the-road-gets-rough-on-your-ride.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/when-the-road-gets-rough-on-your-ride</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:23.813Z</t>
+  </si>
+  <si>
+    <t>When the Road Gets Rough on Your Ride | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/When-the-Road-Gets-Rough-on-Your-Ride.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/which-toyota-can-i-afford.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/which-toyota-can-i-afford</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:42.159Z</t>
+  </si>
+  <si>
+    <t>Which Toyota Can I Afford? | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/which_toyota_can_I_afford.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/which-toyota-is-right-for-you.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/which-toyota-is-right-for-you</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:33.999Z</t>
+  </si>
+  <si>
+    <t>Which Toyota is Right for You? | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/which-toyota-is-right-for-you.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/why-are-toyota-service-centers-a-good-idea.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/why-are-toyota-service-centers-a-good-idea</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:39:49.091Z</t>
+  </si>
+  <si>
+    <t>Why Are Toyota Service Centers a Good Idea? | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/why_are_toyota_service_centers_a_good_idea.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/why-you-should-schedule-a-lease-end-inspection-at-a-toyota-dealership.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/why-you-should-schedule-a-lease-end-inspection-at-a-toyota-dealership</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:28.875Z</t>
+  </si>
+  <si>
+    <t>Why You Should Schedule a Lease-End Inspection at a Toyota Dealership | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Why_You_Should_Schedule_a_Lease-End_Inspection_at_a_Toyota_Dealership.html</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/your-lease-end-invoice.report.json</t>
+  </si>
+  <si>
+    <t>us/en/tfs-thoughtfuel-blog/your-lease-end-invoice</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:37:34.870Z</t>
+  </si>
+  <si>
+    <t>Your Lease-End Invoice | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/TFS_ThoughtFuel_Blog/Your_Lease_End_Invoice.html</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/excess-wear-use-protection.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","video-poster","quiz-plans","carousel-cards"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/excess-wear-use-protection</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:35.012Z</t>
+  </si>
+  <si>
+    <t>Which plan is right for me? | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/excess_wear_use_protection.html</t>
+  </si>
+  <si>
     <t>us/en/vehicle-protection-plan/guaranteed-auto-protection.report.json</t>
   </si>
   <si>
@@ -382,6 +1348,24 @@
     <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/how_to_file_a_claim.html</t>
   </si>
   <si>
+    <t>us/en/vehicle-protection-plan/new-vehicle.report.json</t>
+  </si>
+  <si>
+    <t>["cards-thumbnail","cards-thumbnail","cards-thumbnail","cards-thumbnail","cards-thumbnail","cards-thumbnail","cards-thumbnail","tabs-plans"]</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/new-vehicle</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:41.669Z</t>
+  </si>
+  <si>
+    <t>New Vehicle | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/new_vehicle.html</t>
+  </si>
+  <si>
     <t>us/en/vehicle-protection-plan/prepaid-maintenance-plan.report.json</t>
   </si>
   <si>
@@ -418,6 +1402,21 @@
     <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/tire_wheel_protection.html</t>
   </si>
   <si>
+    <t>us/en/vehicle-protection-plan/used-vehicle.report.json</t>
+  </si>
+  <si>
+    <t>us/en/vehicle-protection-plan/used-vehicle</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:41:48.439Z</t>
+  </si>
+  <si>
+    <t>Used Vehicle | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/used_vehicle.html</t>
+  </si>
+  <si>
     <t>us/en/vehicle-protection-plan/vehicle-service-agreements.report.json</t>
   </si>
   <si>
@@ -439,18 +1438,12 @@
     <t>us/en/vehicle-protection-plan/which-plan-is-right-for-me.report.json</t>
   </si>
   <si>
-    <t>["columns-callout","video-poster","quiz-plans","carousel-cards"]</t>
-  </si>
-  <si>
     <t>us/en/vehicle-protection-plan/which-plan-is-right-for-me</t>
   </si>
   <si>
     <t>2026-10-04T06:02:57.966Z</t>
   </si>
   <si>
-    <t>Which plan is right for me? | Toyota Financial</t>
-  </si>
-  <si>
     <t>https://www.toyotafinancial.com/us/en/vehicle_protection_plan/which_plan_is_right_for_me.html</t>
   </si>
   <si>
@@ -472,18 +1465,12 @@
     <t>us/en/financing-options/for-businesses/business-solutions.report.json</t>
   </si>
   <si>
-    <t>["columns-callout","accordion-faq"]</t>
-  </si>
-  <si>
     <t>us/en/financing-options/for-businesses/business-solutions</t>
   </si>
   <si>
     <t>2026-10-04T06:06:16.167Z</t>
   </si>
   <si>
-    <t>Business Solutions | Toyota Financial</t>
-  </si>
-  <si>
     <t>https://www.toyotafinancial.com/us/en/financing_options/for_businesses/business_solutions.html</t>
   </si>
   <si>
@@ -511,9 +1498,6 @@
     <t>2026-10-04T06:04:51.364Z</t>
   </si>
   <si>
-    <t>Find a Program | Toyota Financial</t>
-  </si>
-  <si>
     <t>https://www.toyotafinancial.com/us/en/financing_options/rebate_finance_programs/find_rebate_finance_programs.html</t>
   </si>
   <si>
@@ -556,9 +1540,6 @@
     <t>2026-10-04T06:06:04.024Z</t>
   </si>
   <si>
-    <t>Credit 101 | Toyota Financial</t>
-  </si>
-  <si>
     <t>https://www.toyotafinancial.com/us/en/financing_options/understanding_credit/credit_101.html</t>
   </si>
   <si>
@@ -575,6 +1556,24 @@
   </si>
   <si>
     <t>https://www.toyotafinancial.com/us/en/financing_options/understanding_credit/credit_tips.html</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/understanding-credit/your-credit.report.json</t>
+  </si>
+  <si>
+    <t>["columns-callout","table-caption"]</t>
+  </si>
+  <si>
+    <t>us/en/financing-options/understanding-credit/your-credit</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:40:17.406Z</t>
+  </si>
+  <si>
+    <t>Your Credit | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/financing_options/understanding_credit/your_credit.html</t>
   </si>
   <si>
     <t>us/en/planning-tools/faq/about-credit.report.json</t>
@@ -1163,6 +2162,39 @@
   </si>
   <si>
     <t>2026-10-03T23:49:41.188Z</t>
+  </si>
+  <si>
+    <t>us/en/planning-tools/faq/guaranteed-auto-protection-gap/how-do-i-withdraw-a-gap-claim.report.json</t>
+  </si>
+  <si>
+    <t>["fragment"]</t>
+  </si>
+  <si>
+    <t>us/en/planning-tools/faq/guaranteed-auto-protection-gap/how-do-i-withdraw-a-gap-claim</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:23:01.639Z</t>
+  </si>
+  <si>
+    <t>How do I withdraw a GAP claim? | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/planning_tools/faq/Guaranteed_Auto_Protection_GAP/How_do_I_withdraw_a_GAP_claim.html</t>
+  </si>
+  <si>
+    <t>us/en/planning-tools/faq/loan-payoff-and-title-lien-release/what-should-i-do-if-i-paid-off-my-loan-but-have-not-received-my-title-lien-release.report.json</t>
+  </si>
+  <si>
+    <t>us/en/planning-tools/faq/loan-payoff-and-title-lien-release/what-should-i-do-if-i-paid-off-my-loan-but-have-not-received-my-title-lien-release</t>
+  </si>
+  <si>
+    <t>2026-10-04T15:23:05.742Z</t>
+  </si>
+  <si>
+    <t>What should I do if I paid off my loan but have not received my title/lien release? | Toyota Financial</t>
+  </si>
+  <si>
+    <t>https://www.toyotafinancial.com/us/en/planning_tools/faq/loan_payoff_and_title_lien_release/What_should_I_do_if_I_paid_off_my_loan_but_have_not_received_my_title_lien_release.html</t>
   </si>
 </sst>
 </file>
@@ -1551,11 +2583,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
@@ -1708,7 +2740,7 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>35</v>
@@ -1725,80 +2757,80 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
         <v>40</v>
       </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>41</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>42</v>
-      </c>
-      <c r="J6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
         <v>45</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="I7" t="s">
         <v>46</v>
       </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>47</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>52</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -1807,245 +2839,245 @@
         <v>22</v>
       </c>
       <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
         <v>53</v>
-      </c>
-      <c r="I8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" t="s">
+      <c r="I9" t="s">
         <v>57</v>
       </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="J9" t="s">
         <v>58</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
         <v>62</v>
       </c>
-      <c r="B10" t="s">
+      <c r="I10" t="s">
         <v>63</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="J10" t="s">
         <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" t="s">
         <v>68</v>
       </c>
-      <c r="B11" t="s">
+      <c r="I11" t="s">
         <v>69</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="J11" t="s">
         <v>70</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
         <v>74</v>
       </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
         <v>75</v>
       </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>76</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>77</v>
-      </c>
-      <c r="I12" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
         <v>80</v>
       </c>
-      <c r="B13" t="s">
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
         <v>81</v>
       </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="I13" t="s">
         <v>82</v>
       </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="J13" t="s">
         <v>83</v>
-      </c>
-      <c r="H13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" t="s">
-        <v>85</v>
-      </c>
-      <c r="J13" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" t="s">
         <v>87</v>
       </c>
-      <c r="B14" t="s">
+      <c r="I14" t="s">
         <v>88</v>
       </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="J14" t="s">
         <v>89</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" t="s">
         <v>94</v>
-      </c>
-      <c r="B15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -2054,653 +3086,653 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" t="s">
         <v>105</v>
-      </c>
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" t="s">
-        <v>108</v>
-      </c>
-      <c r="I17" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" t="s">
+        <v>110</v>
+      </c>
+      <c r="J18" t="s">
         <v>111</v>
-      </c>
-      <c r="B18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" t="s">
-        <v>115</v>
-      </c>
-      <c r="J18" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" t="s">
         <v>117</v>
-      </c>
-      <c r="B19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" t="s">
-        <v>120</v>
-      </c>
-      <c r="I19" t="s">
-        <v>121</v>
-      </c>
-      <c r="J19" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" t="s">
         <v>123</v>
       </c>
-      <c r="B20" t="s">
+      <c r="J20" t="s">
         <v>124</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
-        <v>125</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" t="s">
-        <v>126</v>
-      </c>
-      <c r="I20" t="s">
-        <v>127</v>
-      </c>
-      <c r="J20" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" t="s">
         <v>129</v>
       </c>
-      <c r="B21" t="s">
+      <c r="J21" t="s">
         <v>130</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>131</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" t="s">
-        <v>132</v>
-      </c>
-      <c r="I21" t="s">
-        <v>133</v>
-      </c>
-      <c r="J21" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" t="s">
         <v>135</v>
       </c>
-      <c r="B22" t="s">
+      <c r="J22" t="s">
         <v>136</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>137</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" t="s">
-        <v>138</v>
-      </c>
-      <c r="I22" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" t="s">
         <v>141</v>
       </c>
-      <c r="B23" t="s">
+      <c r="J23" t="s">
         <v>142</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>143</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" t="s">
-        <v>144</v>
-      </c>
-      <c r="I23" t="s">
-        <v>145</v>
-      </c>
-      <c r="J23" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" t="s">
         <v>147</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>148</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H24" t="s">
-        <v>149</v>
-      </c>
-      <c r="I24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J24" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" t="s">
         <v>152</v>
-      </c>
-      <c r="B25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" t="s">
-        <v>155</v>
-      </c>
-      <c r="I25" t="s">
-        <v>156</v>
-      </c>
-      <c r="J25" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>155</v>
+      </c>
+      <c r="H26" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" t="s">
+        <v>157</v>
+      </c>
+      <c r="J26" t="s">
         <v>158</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" t="s">
-        <v>159</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s">
-        <v>29</v>
-      </c>
-      <c r="H26" t="s">
-        <v>160</v>
-      </c>
-      <c r="I26" t="s">
-        <v>161</v>
-      </c>
-      <c r="J26" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H27" t="s">
+        <v>162</v>
+      </c>
+      <c r="I27" t="s">
         <v>163</v>
       </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="J27" t="s">
         <v>164</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s">
-        <v>29</v>
-      </c>
-      <c r="H27" t="s">
-        <v>165</v>
-      </c>
-      <c r="I27" t="s">
-        <v>166</v>
-      </c>
-      <c r="J27" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
         <v>168</v>
       </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="H28" t="s">
         <v>169</v>
       </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>170</v>
       </c>
-      <c r="I28" t="s">
-        <v>171</v>
-      </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
         <v>173</v>
       </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="I29" t="s">
         <v>174</v>
       </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>29</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>175</v>
-      </c>
-      <c r="I29" t="s">
-        <v>176</v>
-      </c>
-      <c r="J29" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" t="s">
         <v>178</v>
       </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="I30" t="s">
         <v>179</v>
       </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" t="s">
-        <v>29</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
         <v>180</v>
-      </c>
-      <c r="I30" t="s">
-        <v>181</v>
-      </c>
-      <c r="J30" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
         <v>183</v>
       </c>
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="I31" t="s">
         <v>184</v>
       </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="J31" t="s">
         <v>185</v>
-      </c>
-      <c r="I31" t="s">
-        <v>186</v>
-      </c>
-      <c r="J31" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" t="s">
         <v>188</v>
       </c>
-      <c r="B32" t="s">
+      <c r="I32" t="s">
         <v>189</v>
       </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="J32" t="s">
         <v>190</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" t="s">
-        <v>191</v>
-      </c>
-      <c r="H32" t="s">
-        <v>192</v>
-      </c>
-      <c r="I32" t="s">
-        <v>193</v>
-      </c>
-      <c r="J32" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>191</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" t="s">
+        <v>193</v>
+      </c>
+      <c r="I33" t="s">
+        <v>194</v>
+      </c>
+      <c r="J33" t="s">
         <v>195</v>
-      </c>
-      <c r="B33" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" t="s">
-        <v>196</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" t="s">
-        <v>191</v>
-      </c>
-      <c r="H33" t="s">
-        <v>197</v>
-      </c>
-      <c r="I33" t="s">
-        <v>198</v>
-      </c>
-      <c r="J33" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" t="s">
+        <v>199</v>
+      </c>
+      <c r="J34" t="s">
         <v>200</v>
-      </c>
-      <c r="B34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
-        <v>201</v>
-      </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" t="s">
-        <v>191</v>
-      </c>
-      <c r="H34" t="s">
-        <v>202</v>
-      </c>
-      <c r="I34" t="s">
-        <v>203</v>
-      </c>
-      <c r="J34" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>204</v>
+      </c>
+      <c r="H35" t="s">
         <v>205</v>
       </c>
-      <c r="B35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="I35" t="s">
         <v>206</v>
       </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" t="s">
-        <v>191</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>207</v>
-      </c>
-      <c r="I35" t="s">
-        <v>208</v>
-      </c>
-      <c r="J35" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
         <v>210</v>
       </c>
-      <c r="B36" t="s">
-        <v>189</v>
-      </c>
-      <c r="C36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
         <v>211</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" t="s">
-        <v>191</v>
       </c>
       <c r="H36" t="s">
         <v>212</v>
@@ -2717,7 +3749,7 @@
         <v>215</v>
       </c>
       <c r="B37" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2726,30 +3758,30 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H37" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2758,30 +3790,30 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B39" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2790,30 +3822,30 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H39" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I39" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="J39" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B40" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2822,30 +3854,30 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H40" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I40" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J40" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2854,30 +3886,30 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H41" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I41" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J41" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -2886,30 +3918,30 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H42" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I42" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J42" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B43" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -2918,30 +3950,30 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H43" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I43" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J43" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -2950,30 +3982,30 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H44" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="I44" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="J44" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -2982,30 +4014,30 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H45" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I45" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="J45" t="s">
-        <v>258</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B46" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -3014,30 +4046,30 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H46" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I46" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="J46" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -3046,30 +4078,30 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H47" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I47" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J47" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -3078,30 +4110,30 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H48" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="I48" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J48" t="s">
-        <v>79</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B49" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
@@ -3110,30 +4142,30 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H49" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="I49" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="J49" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -3142,30 +4174,30 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H50" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="I50" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="J50" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -3174,30 +4206,30 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H51" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I51" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="J51" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
@@ -3206,30 +4238,30 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H52" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I52" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="J52" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B53" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -3238,30 +4270,30 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H53" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="I53" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="J53" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B54" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -3270,30 +4302,30 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H54" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I54" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J54" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B55" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
@@ -3302,30 +4334,30 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H55" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I55" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="J55" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B56" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -3334,30 +4366,30 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H56" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="I56" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="J56" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B57" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -3366,30 +4398,30 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H57" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I57" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="J57" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -3398,30 +4430,30 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H58" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I58" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="J58" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -3430,30 +4462,30 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H59" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="I59" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="J59" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B60" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
@@ -3462,30 +4494,30 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H60" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I60" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="J60" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B61" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -3494,30 +4526,30 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H61" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="I61" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="J61" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B62" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -3526,30 +4558,30 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H62" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="I62" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="J62" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -3558,30 +4590,30 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H63" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="I63" t="s">
-        <v>345</v>
+        <v>271</v>
       </c>
       <c r="J63" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B64" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
@@ -3590,30 +4622,30 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H64" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="I64" t="s">
-        <v>176</v>
+        <v>355</v>
       </c>
       <c r="J64" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -3622,30 +4654,30 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H65" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I65" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="J65" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C66" t="s">
         <v>12</v>
@@ -3654,30 +4686,30 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H66" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I66" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J66" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B67" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
@@ -3686,30 +4718,30 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H67" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="I67" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="J67" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B68" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -3718,30 +4750,30 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H68" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="I68" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="J68" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B69" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -3750,54 +4782,2198 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="H69" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="I69" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="J69" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>233</v>
       </c>
       <c r="C70" t="s">
-        <v>377</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>378</v>
+        <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F70" t="s">
-        <v>380</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H70" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I70" t="s">
-        <v>12</v>
+        <v>385</v>
       </c>
       <c r="J70" t="s">
-        <v>194</v>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>387</v>
+      </c>
+      <c r="B71" t="s">
+        <v>249</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" t="s">
+        <v>388</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" t="s">
+        <v>389</v>
+      </c>
+      <c r="I71" t="s">
+        <v>390</v>
+      </c>
+      <c r="J71" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>392</v>
+      </c>
+      <c r="B72" t="s">
+        <v>233</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" t="s">
+        <v>393</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" t="s">
+        <v>394</v>
+      </c>
+      <c r="I72" t="s">
+        <v>395</v>
+      </c>
+      <c r="J72" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>397</v>
+      </c>
+      <c r="B73" t="s">
+        <v>233</v>
+      </c>
+      <c r="C73" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" t="s">
+        <v>398</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73" t="s">
+        <v>399</v>
+      </c>
+      <c r="I73" t="s">
+        <v>400</v>
+      </c>
+      <c r="J73" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>402</v>
+      </c>
+      <c r="B74" t="s">
+        <v>249</v>
+      </c>
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" t="s">
+        <v>403</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>29</v>
+      </c>
+      <c r="H74" t="s">
+        <v>404</v>
+      </c>
+      <c r="I74" t="s">
+        <v>405</v>
+      </c>
+      <c r="J74" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>407</v>
+      </c>
+      <c r="B75" t="s">
+        <v>233</v>
+      </c>
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" t="s">
+        <v>408</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>29</v>
+      </c>
+      <c r="H75" t="s">
+        <v>409</v>
+      </c>
+      <c r="I75" t="s">
+        <v>410</v>
+      </c>
+      <c r="J75" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>412</v>
+      </c>
+      <c r="B76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" t="s">
+        <v>413</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>29</v>
+      </c>
+      <c r="H76" t="s">
+        <v>414</v>
+      </c>
+      <c r="I76" t="s">
+        <v>415</v>
+      </c>
+      <c r="J76" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>417</v>
+      </c>
+      <c r="B77" t="s">
+        <v>233</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" t="s">
+        <v>418</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77" t="s">
+        <v>419</v>
+      </c>
+      <c r="I77" t="s">
+        <v>420</v>
+      </c>
+      <c r="J77" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>422</v>
+      </c>
+      <c r="B78" t="s">
+        <v>233</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>423</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>29</v>
+      </c>
+      <c r="H78" t="s">
+        <v>424</v>
+      </c>
+      <c r="I78" t="s">
+        <v>425</v>
+      </c>
+      <c r="J78" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>427</v>
+      </c>
+      <c r="B79" t="s">
+        <v>428</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>429</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" t="s">
+        <v>430</v>
+      </c>
+      <c r="I79" t="s">
+        <v>431</v>
+      </c>
+      <c r="J79" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>433</v>
+      </c>
+      <c r="B80" t="s">
+        <v>434</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" t="s">
+        <v>435</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>29</v>
+      </c>
+      <c r="H80" t="s">
+        <v>436</v>
+      </c>
+      <c r="I80" t="s">
+        <v>437</v>
+      </c>
+      <c r="J80" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>439</v>
+      </c>
+      <c r="B81" t="s">
+        <v>440</v>
+      </c>
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" t="s">
+        <v>441</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>29</v>
+      </c>
+      <c r="H81" t="s">
+        <v>442</v>
+      </c>
+      <c r="I81" t="s">
+        <v>443</v>
+      </c>
+      <c r="J81" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>445</v>
+      </c>
+      <c r="B82" t="s">
+        <v>446</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" t="s">
+        <v>447</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>29</v>
+      </c>
+      <c r="H82" t="s">
+        <v>448</v>
+      </c>
+      <c r="I82" t="s">
+        <v>449</v>
+      </c>
+      <c r="J82" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>451</v>
+      </c>
+      <c r="B83" t="s">
+        <v>452</v>
+      </c>
+      <c r="C83" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" t="s">
+        <v>453</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>29</v>
+      </c>
+      <c r="H83" t="s">
+        <v>454</v>
+      </c>
+      <c r="I83" t="s">
+        <v>455</v>
+      </c>
+      <c r="J83" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>457</v>
+      </c>
+      <c r="B84" t="s">
+        <v>458</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" t="s">
+        <v>459</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" t="s">
+        <v>29</v>
+      </c>
+      <c r="H84" t="s">
+        <v>460</v>
+      </c>
+      <c r="I84" t="s">
+        <v>461</v>
+      </c>
+      <c r="J84" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>463</v>
+      </c>
+      <c r="B85" t="s">
+        <v>446</v>
+      </c>
+      <c r="C85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" t="s">
+        <v>464</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>29</v>
+      </c>
+      <c r="H85" t="s">
+        <v>465</v>
+      </c>
+      <c r="I85" t="s">
+        <v>466</v>
+      </c>
+      <c r="J85" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>468</v>
+      </c>
+      <c r="B86" t="s">
+        <v>469</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" t="s">
+        <v>470</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
+        <v>29</v>
+      </c>
+      <c r="H86" t="s">
+        <v>471</v>
+      </c>
+      <c r="I86" t="s">
+        <v>472</v>
+      </c>
+      <c r="J86" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>474</v>
+      </c>
+      <c r="B87" t="s">
+        <v>428</v>
+      </c>
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" t="s">
+        <v>475</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" t="s">
+        <v>29</v>
+      </c>
+      <c r="H87" t="s">
+        <v>476</v>
+      </c>
+      <c r="I87" t="s">
+        <v>431</v>
+      </c>
+      <c r="J87" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>478</v>
+      </c>
+      <c r="B88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" t="s">
+        <v>479</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" t="s">
+        <v>29</v>
+      </c>
+      <c r="H88" t="s">
+        <v>480</v>
+      </c>
+      <c r="I88" t="s">
+        <v>481</v>
+      </c>
+      <c r="J88" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>483</v>
+      </c>
+      <c r="B89" t="s">
+        <v>126</v>
+      </c>
+      <c r="C89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" t="s">
+        <v>484</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" t="s">
+        <v>29</v>
+      </c>
+      <c r="H89" t="s">
+        <v>485</v>
+      </c>
+      <c r="I89" t="s">
+        <v>129</v>
+      </c>
+      <c r="J89" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>487</v>
+      </c>
+      <c r="B90" t="s">
+        <v>138</v>
+      </c>
+      <c r="C90" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" t="s">
+        <v>488</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" t="s">
+        <v>29</v>
+      </c>
+      <c r="H90" t="s">
+        <v>489</v>
+      </c>
+      <c r="I90" t="s">
+        <v>490</v>
+      </c>
+      <c r="J90" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>492</v>
+      </c>
+      <c r="B91" t="s">
+        <v>138</v>
+      </c>
+      <c r="C91" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" t="s">
+        <v>493</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" t="s">
+        <v>29</v>
+      </c>
+      <c r="H91" t="s">
+        <v>494</v>
+      </c>
+      <c r="I91" t="s">
+        <v>141</v>
+      </c>
+      <c r="J91" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>496</v>
+      </c>
+      <c r="B92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" t="s">
+        <v>497</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" t="s">
+        <v>29</v>
+      </c>
+      <c r="H92" t="s">
+        <v>498</v>
+      </c>
+      <c r="I92" t="s">
+        <v>499</v>
+      </c>
+      <c r="J92" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>501</v>
+      </c>
+      <c r="B93" t="s">
+        <v>138</v>
+      </c>
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" t="s">
+        <v>502</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" t="s">
+        <v>29</v>
+      </c>
+      <c r="H93" t="s">
+        <v>503</v>
+      </c>
+      <c r="I93" t="s">
+        <v>504</v>
+      </c>
+      <c r="J93" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>506</v>
+      </c>
+      <c r="B94" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" t="s">
+        <v>507</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" t="s">
+        <v>29</v>
+      </c>
+      <c r="H94" t="s">
+        <v>508</v>
+      </c>
+      <c r="I94" t="s">
+        <v>151</v>
+      </c>
+      <c r="J94" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>510</v>
+      </c>
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" t="s">
+        <v>511</v>
+      </c>
+      <c r="F95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" t="s">
+        <v>29</v>
+      </c>
+      <c r="H95" t="s">
+        <v>512</v>
+      </c>
+      <c r="I95" t="s">
+        <v>513</v>
+      </c>
+      <c r="J95" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>515</v>
+      </c>
+      <c r="B96" t="s">
+        <v>516</v>
+      </c>
+      <c r="C96" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" t="s">
+        <v>517</v>
+      </c>
+      <c r="F96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" t="s">
+        <v>29</v>
+      </c>
+      <c r="H96" t="s">
+        <v>518</v>
+      </c>
+      <c r="I96" t="s">
+        <v>519</v>
+      </c>
+      <c r="J96" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>521</v>
+      </c>
+      <c r="B97" t="s">
+        <v>522</v>
+      </c>
+      <c r="C97" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" t="s">
+        <v>523</v>
+      </c>
+      <c r="F97" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" t="s">
+        <v>524</v>
+      </c>
+      <c r="H97" t="s">
+        <v>525</v>
+      </c>
+      <c r="I97" t="s">
+        <v>526</v>
+      </c>
+      <c r="J97" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>528</v>
+      </c>
+      <c r="B98" t="s">
+        <v>522</v>
+      </c>
+      <c r="C98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" t="s">
+        <v>529</v>
+      </c>
+      <c r="F98" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98" t="s">
+        <v>524</v>
+      </c>
+      <c r="H98" t="s">
+        <v>530</v>
+      </c>
+      <c r="I98" t="s">
+        <v>531</v>
+      </c>
+      <c r="J98" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>533</v>
+      </c>
+      <c r="B99" t="s">
+        <v>522</v>
+      </c>
+      <c r="C99" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" t="s">
+        <v>534</v>
+      </c>
+      <c r="F99" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" t="s">
+        <v>524</v>
+      </c>
+      <c r="H99" t="s">
+        <v>535</v>
+      </c>
+      <c r="I99" t="s">
+        <v>536</v>
+      </c>
+      <c r="J99" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>538</v>
+      </c>
+      <c r="B100" t="s">
+        <v>522</v>
+      </c>
+      <c r="C100" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" t="s">
+        <v>539</v>
+      </c>
+      <c r="F100" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" t="s">
+        <v>524</v>
+      </c>
+      <c r="H100" t="s">
+        <v>540</v>
+      </c>
+      <c r="I100" t="s">
+        <v>541</v>
+      </c>
+      <c r="J100" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>543</v>
+      </c>
+      <c r="B101" t="s">
+        <v>522</v>
+      </c>
+      <c r="C101" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" t="s">
+        <v>544</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" t="s">
+        <v>524</v>
+      </c>
+      <c r="H101" t="s">
+        <v>545</v>
+      </c>
+      <c r="I101" t="s">
+        <v>546</v>
+      </c>
+      <c r="J101" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>548</v>
+      </c>
+      <c r="B102" t="s">
+        <v>522</v>
+      </c>
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" t="s">
+        <v>549</v>
+      </c>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" t="s">
+        <v>524</v>
+      </c>
+      <c r="H102" t="s">
+        <v>550</v>
+      </c>
+      <c r="I102" t="s">
+        <v>551</v>
+      </c>
+      <c r="J102" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>553</v>
+      </c>
+      <c r="B103" t="s">
+        <v>522</v>
+      </c>
+      <c r="C103" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" t="s">
+        <v>554</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>524</v>
+      </c>
+      <c r="H103" t="s">
+        <v>555</v>
+      </c>
+      <c r="I103" t="s">
+        <v>556</v>
+      </c>
+      <c r="J103" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>558</v>
+      </c>
+      <c r="B104" t="s">
+        <v>522</v>
+      </c>
+      <c r="C104" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" t="s">
+        <v>559</v>
+      </c>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>524</v>
+      </c>
+      <c r="H104" t="s">
+        <v>560</v>
+      </c>
+      <c r="I104" t="s">
+        <v>129</v>
+      </c>
+      <c r="J104" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>562</v>
+      </c>
+      <c r="B105" t="s">
+        <v>522</v>
+      </c>
+      <c r="C105" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105" t="s">
+        <v>563</v>
+      </c>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>524</v>
+      </c>
+      <c r="H105" t="s">
+        <v>564</v>
+      </c>
+      <c r="I105" t="s">
+        <v>565</v>
+      </c>
+      <c r="J105" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>567</v>
+      </c>
+      <c r="B106" t="s">
+        <v>522</v>
+      </c>
+      <c r="C106" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" t="s">
+        <v>568</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>524</v>
+      </c>
+      <c r="H106" t="s">
+        <v>569</v>
+      </c>
+      <c r="I106" t="s">
+        <v>570</v>
+      </c>
+      <c r="J106" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>572</v>
+      </c>
+      <c r="B107" t="s">
+        <v>522</v>
+      </c>
+      <c r="C107" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" t="s">
+        <v>573</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>524</v>
+      </c>
+      <c r="H107" t="s">
+        <v>574</v>
+      </c>
+      <c r="I107" t="s">
+        <v>575</v>
+      </c>
+      <c r="J107" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>577</v>
+      </c>
+      <c r="B108" t="s">
+        <v>522</v>
+      </c>
+      <c r="C108" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" t="s">
+        <v>578</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>524</v>
+      </c>
+      <c r="H108" t="s">
+        <v>579</v>
+      </c>
+      <c r="I108" t="s">
+        <v>580</v>
+      </c>
+      <c r="J108" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>582</v>
+      </c>
+      <c r="B109" t="s">
+        <v>522</v>
+      </c>
+      <c r="C109" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109" t="s">
+        <v>583</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>524</v>
+      </c>
+      <c r="H109" t="s">
+        <v>584</v>
+      </c>
+      <c r="I109" t="s">
+        <v>585</v>
+      </c>
+      <c r="J109" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>587</v>
+      </c>
+      <c r="B110" t="s">
+        <v>522</v>
+      </c>
+      <c r="C110" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110" t="s">
+        <v>588</v>
+      </c>
+      <c r="F110" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>524</v>
+      </c>
+      <c r="H110" t="s">
+        <v>589</v>
+      </c>
+      <c r="I110" t="s">
+        <v>590</v>
+      </c>
+      <c r="J110" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>592</v>
+      </c>
+      <c r="B111" t="s">
+        <v>522</v>
+      </c>
+      <c r="C111" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" t="s">
+        <v>593</v>
+      </c>
+      <c r="F111" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111" t="s">
+        <v>524</v>
+      </c>
+      <c r="H111" t="s">
+        <v>594</v>
+      </c>
+      <c r="I111" t="s">
+        <v>472</v>
+      </c>
+      <c r="J111" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>596</v>
+      </c>
+      <c r="B112" t="s">
+        <v>522</v>
+      </c>
+      <c r="C112" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" t="s">
+        <v>597</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>524</v>
+      </c>
+      <c r="H112" t="s">
+        <v>598</v>
+      </c>
+      <c r="I112" t="s">
+        <v>599</v>
+      </c>
+      <c r="J112" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>601</v>
+      </c>
+      <c r="B113" t="s">
+        <v>522</v>
+      </c>
+      <c r="C113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" t="s">
+        <v>602</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>524</v>
+      </c>
+      <c r="H113" t="s">
+        <v>603</v>
+      </c>
+      <c r="I113" t="s">
+        <v>604</v>
+      </c>
+      <c r="J113" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>605</v>
+      </c>
+      <c r="B114" t="s">
+        <v>522</v>
+      </c>
+      <c r="C114" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" t="s">
+        <v>606</v>
+      </c>
+      <c r="F114" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114" t="s">
+        <v>524</v>
+      </c>
+      <c r="H114" t="s">
+        <v>607</v>
+      </c>
+      <c r="I114" t="s">
+        <v>608</v>
+      </c>
+      <c r="J114" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>610</v>
+      </c>
+      <c r="B115" t="s">
+        <v>522</v>
+      </c>
+      <c r="C115" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" t="s">
+        <v>611</v>
+      </c>
+      <c r="F115" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" t="s">
+        <v>524</v>
+      </c>
+      <c r="H115" t="s">
+        <v>612</v>
+      </c>
+      <c r="I115" t="s">
+        <v>613</v>
+      </c>
+      <c r="J115" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>615</v>
+      </c>
+      <c r="B116" t="s">
+        <v>522</v>
+      </c>
+      <c r="C116" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" t="s">
+        <v>616</v>
+      </c>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" t="s">
+        <v>524</v>
+      </c>
+      <c r="H116" t="s">
+        <v>617</v>
+      </c>
+      <c r="I116" t="s">
+        <v>618</v>
+      </c>
+      <c r="J116" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>620</v>
+      </c>
+      <c r="B117" t="s">
+        <v>522</v>
+      </c>
+      <c r="C117" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" t="s">
+        <v>621</v>
+      </c>
+      <c r="F117" t="s">
+        <v>14</v>
+      </c>
+      <c r="G117" t="s">
+        <v>524</v>
+      </c>
+      <c r="H117" t="s">
+        <v>622</v>
+      </c>
+      <c r="I117" t="s">
+        <v>623</v>
+      </c>
+      <c r="J117" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>625</v>
+      </c>
+      <c r="B118" t="s">
+        <v>522</v>
+      </c>
+      <c r="C118" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" t="s">
+        <v>626</v>
+      </c>
+      <c r="F118" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" t="s">
+        <v>524</v>
+      </c>
+      <c r="H118" t="s">
+        <v>627</v>
+      </c>
+      <c r="I118" t="s">
+        <v>628</v>
+      </c>
+      <c r="J118" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>630</v>
+      </c>
+      <c r="B119" t="s">
+        <v>522</v>
+      </c>
+      <c r="C119" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" t="s">
+        <v>631</v>
+      </c>
+      <c r="F119" t="s">
+        <v>14</v>
+      </c>
+      <c r="G119" t="s">
+        <v>524</v>
+      </c>
+      <c r="H119" t="s">
+        <v>632</v>
+      </c>
+      <c r="I119" t="s">
+        <v>633</v>
+      </c>
+      <c r="J119" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>635</v>
+      </c>
+      <c r="B120" t="s">
+        <v>522</v>
+      </c>
+      <c r="C120" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" t="s">
+        <v>636</v>
+      </c>
+      <c r="F120" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s">
+        <v>524</v>
+      </c>
+      <c r="H120" t="s">
+        <v>637</v>
+      </c>
+      <c r="I120" t="s">
+        <v>638</v>
+      </c>
+      <c r="J120" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>640</v>
+      </c>
+      <c r="B121" t="s">
+        <v>522</v>
+      </c>
+      <c r="C121" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" t="s">
+        <v>641</v>
+      </c>
+      <c r="F121" t="s">
+        <v>14</v>
+      </c>
+      <c r="G121" t="s">
+        <v>524</v>
+      </c>
+      <c r="H121" t="s">
+        <v>642</v>
+      </c>
+      <c r="I121" t="s">
+        <v>643</v>
+      </c>
+      <c r="J121" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>645</v>
+      </c>
+      <c r="B122" t="s">
+        <v>522</v>
+      </c>
+      <c r="C122" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" t="s">
+        <v>646</v>
+      </c>
+      <c r="F122" t="s">
+        <v>14</v>
+      </c>
+      <c r="G122" t="s">
+        <v>524</v>
+      </c>
+      <c r="H122" t="s">
+        <v>647</v>
+      </c>
+      <c r="I122" t="s">
+        <v>648</v>
+      </c>
+      <c r="J122" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>650</v>
+      </c>
+      <c r="B123" t="s">
+        <v>522</v>
+      </c>
+      <c r="C123" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" t="s">
+        <v>651</v>
+      </c>
+      <c r="F123" t="s">
+        <v>14</v>
+      </c>
+      <c r="G123" t="s">
+        <v>524</v>
+      </c>
+      <c r="H123" t="s">
+        <v>652</v>
+      </c>
+      <c r="I123" t="s">
+        <v>653</v>
+      </c>
+      <c r="J123" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>655</v>
+      </c>
+      <c r="B124" t="s">
+        <v>522</v>
+      </c>
+      <c r="C124" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" t="s">
+        <v>656</v>
+      </c>
+      <c r="F124" t="s">
+        <v>14</v>
+      </c>
+      <c r="G124" t="s">
+        <v>524</v>
+      </c>
+      <c r="H124" t="s">
+        <v>657</v>
+      </c>
+      <c r="I124" t="s">
+        <v>658</v>
+      </c>
+      <c r="J124" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>660</v>
+      </c>
+      <c r="B125" t="s">
+        <v>522</v>
+      </c>
+      <c r="C125" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" t="s">
+        <v>661</v>
+      </c>
+      <c r="F125" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" t="s">
+        <v>524</v>
+      </c>
+      <c r="H125" t="s">
+        <v>662</v>
+      </c>
+      <c r="I125" t="s">
+        <v>663</v>
+      </c>
+      <c r="J125" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>665</v>
+      </c>
+      <c r="B126" t="s">
+        <v>522</v>
+      </c>
+      <c r="C126" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" t="s">
+        <v>666</v>
+      </c>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126" t="s">
+        <v>524</v>
+      </c>
+      <c r="H126" t="s">
+        <v>667</v>
+      </c>
+      <c r="I126" t="s">
+        <v>668</v>
+      </c>
+      <c r="J126" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>670</v>
+      </c>
+      <c r="B127" t="s">
+        <v>522</v>
+      </c>
+      <c r="C127" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" t="s">
+        <v>671</v>
+      </c>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" t="s">
+        <v>524</v>
+      </c>
+      <c r="H127" t="s">
+        <v>672</v>
+      </c>
+      <c r="I127" t="s">
+        <v>673</v>
+      </c>
+      <c r="J127" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>675</v>
+      </c>
+      <c r="B128" t="s">
+        <v>522</v>
+      </c>
+      <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" t="s">
+        <v>676</v>
+      </c>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" t="s">
+        <v>524</v>
+      </c>
+      <c r="H128" t="s">
+        <v>677</v>
+      </c>
+      <c r="I128" t="s">
+        <v>678</v>
+      </c>
+      <c r="J128" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>680</v>
+      </c>
+      <c r="B129" t="s">
+        <v>522</v>
+      </c>
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" t="s">
+        <v>681</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" t="s">
+        <v>524</v>
+      </c>
+      <c r="H129" t="s">
+        <v>682</v>
+      </c>
+      <c r="I129" t="s">
+        <v>504</v>
+      </c>
+      <c r="J129" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>684</v>
+      </c>
+      <c r="B130" t="s">
+        <v>522</v>
+      </c>
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" t="s">
+        <v>685</v>
+      </c>
+      <c r="F130" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" t="s">
+        <v>524</v>
+      </c>
+      <c r="H130" t="s">
+        <v>686</v>
+      </c>
+      <c r="I130" t="s">
+        <v>687</v>
+      </c>
+      <c r="J130" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>689</v>
+      </c>
+      <c r="B131" t="s">
+        <v>522</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" t="s">
+        <v>690</v>
+      </c>
+      <c r="F131" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131" t="s">
+        <v>524</v>
+      </c>
+      <c r="H131" t="s">
+        <v>691</v>
+      </c>
+      <c r="I131" t="s">
+        <v>692</v>
+      </c>
+      <c r="J131" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>694</v>
+      </c>
+      <c r="B132" t="s">
+        <v>522</v>
+      </c>
+      <c r="C132" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" t="s">
+        <v>695</v>
+      </c>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" t="s">
+        <v>524</v>
+      </c>
+      <c r="H132" t="s">
+        <v>696</v>
+      </c>
+      <c r="I132" t="s">
+        <v>697</v>
+      </c>
+      <c r="J132" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>699</v>
+      </c>
+      <c r="B133" t="s">
+        <v>522</v>
+      </c>
+      <c r="C133" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" t="s">
+        <v>700</v>
+      </c>
+      <c r="F133" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" t="s">
+        <v>524</v>
+      </c>
+      <c r="H133" t="s">
+        <v>701</v>
+      </c>
+      <c r="I133" t="s">
+        <v>702</v>
+      </c>
+      <c r="J133" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>704</v>
+      </c>
+      <c r="B134" t="s">
+        <v>522</v>
+      </c>
+      <c r="C134" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" t="s">
+        <v>705</v>
+      </c>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>524</v>
+      </c>
+      <c r="H134" t="s">
+        <v>706</v>
+      </c>
+      <c r="I134" t="s">
+        <v>707</v>
+      </c>
+      <c r="J134" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>709</v>
+      </c>
+      <c r="B135" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" t="s">
+        <v>710</v>
+      </c>
+      <c r="D135" t="s">
+        <v>711</v>
+      </c>
+      <c r="E135" t="s">
+        <v>712</v>
+      </c>
+      <c r="F135" t="s">
+        <v>713</v>
+      </c>
+      <c r="G135" t="s">
+        <v>12</v>
+      </c>
+      <c r="H135" t="s">
+        <v>714</v>
+      </c>
+      <c r="I135" t="s">
+        <v>12</v>
+      </c>
+      <c r="J135" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>715</v>
+      </c>
+      <c r="B136" t="s">
+        <v>716</v>
+      </c>
+      <c r="C136" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" t="s">
+        <v>717</v>
+      </c>
+      <c r="F136" t="s">
+        <v>14</v>
+      </c>
+      <c r="G136" t="s">
+        <v>524</v>
+      </c>
+      <c r="H136" t="s">
+        <v>718</v>
+      </c>
+      <c r="I136" t="s">
+        <v>719</v>
+      </c>
+      <c r="J136" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>721</v>
+      </c>
+      <c r="B137" t="s">
+        <v>716</v>
+      </c>
+      <c r="C137" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" t="s">
+        <v>722</v>
+      </c>
+      <c r="F137" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" t="s">
+        <v>524</v>
+      </c>
+      <c r="H137" t="s">
+        <v>723</v>
+      </c>
+      <c r="I137" t="s">
+        <v>724</v>
+      </c>
+      <c r="J137" t="s">
+        <v>725</v>
       </c>
     </row>
   </sheetData>
